--- a/ig/DM-MARS-2026/CodeSystem-concept-properties.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-concept-properties.xlsx
@@ -211,7 +211,7 @@
     <t>Specialisation RPPS</t>
   </si>
   <si>
-    <t>Permet de définir les codes concepts définis par le RPPS</t>
+    <t>Propriété permettant de spécifier les codes exclusifs appartenant au RPPS</t>
   </si>
   <si>
     <t>ror</t>
@@ -286,7 +286,7 @@
     <t>Macro-etat administratif</t>
   </si>
   <si>
-    <t>Macro-état administratif (actif ou inactif) du code concept</t>
+    <t>Propriété permettant de préciser le macro état de chaque objet. Cette propriété est de type Coding et les valeurs possible proviennent de la Tre R386 Macro Etat Objet Administratif</t>
   </si>
   <si>
     <t>hasTypeRoleMember</t>
